--- a/www/download/IND.labour_force_value.s.mv.WIOD16.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7764.503</t>
+          <t>7763855029.3364</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7503.799</t>
+          <t>7502131688.50156</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8457.233</t>
+          <t>8455920992.25034</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10040.125</t>
+          <t>10038813928.5239</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11367.001</t>
+          <t>11365353272.4834</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12068.206</t>
+          <t>12067449749.7004</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11916.569</t>
+          <t>11916145785.7084</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12531.276</t>
+          <t>12529100116.5339</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>11151.936</t>
+          <t>11151778638.2739</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>11692.191</t>
+          <t>11691809045.945</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12504.397</t>
+          <t>12502505813.9246</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>14349.03</t>
+          <t>14344501540.7826</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13906.06</t>
+          <t>13904667885.4931</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>14096.14</t>
+          <t>14095635920.8345</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>13950.343</t>
+          <t>13951617533.9636</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3027.425</t>
+          <t>3027227237.59319</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2946.77</t>
+          <t>2946781245.94175</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2900.745</t>
+          <t>2900274780.40219</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3078.537</t>
+          <t>3077933665.06994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3121.276</t>
+          <t>3121035821.15395</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3058.965</t>
+          <t>3059126644.23285</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3182.359</t>
+          <t>3182267596.60296</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3182.3</t>
+          <t>3181381113.84232</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3209.638</t>
+          <t>3209158668.66579</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3123.117</t>
+          <t>3122868973.06876</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3003.913</t>
+          <t>3003491852.86716</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3114.545</t>
+          <t>3114008488.88722</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3196.144</t>
+          <t>3195907870.90183</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3455.526</t>
+          <t>3455503857.67461</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3446.633</t>
+          <t>3446695395.20427</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7163.601</t>
+          <t>7162393135.56398</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7350.318</t>
+          <t>7349458048.82628</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7636.713</t>
+          <t>7635367012.97682</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>8634.043</t>
+          <t>8632907122.70579</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>9440.116</t>
+          <t>9439834765.35768</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>9177.247</t>
+          <t>9177118817.00285</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8761.701</t>
+          <t>8761733731.08324</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>8647.729</t>
+          <t>8646439169.49704</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8564.086</t>
+          <t>8563683342.78833</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7829.196</t>
+          <t>7828853802.50521</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5885.795</t>
+          <t>5885163588.10438</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>6092.621</t>
+          <t>6091872431.68289</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5769.386</t>
+          <t>5769033229.90522</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>6140.795</t>
+          <t>6140767627.8418</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6436.847</t>
+          <t>6439963577.35535</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1361.278</t>
+          <t>1361250565.91597</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1337.909</t>
+          <t>1337839028.43169</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1306.408</t>
+          <t>1306332186.74602</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1312.467</t>
+          <t>1312415350.94269</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1274.69</t>
+          <t>1274680832.33803</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1243.401</t>
+          <t>1243385955.20143</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1310.306</t>
+          <t>1310235111.62019</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1249.538</t>
+          <t>1249439672.15839</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1282.109</t>
+          <t>1282139191.83221</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1378.897</t>
+          <t>1378846260.15338</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1216.608</t>
+          <t>1216512650.00853</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1143.576</t>
+          <t>1143457206.85727</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1164.707</t>
+          <t>1164655426.1322</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1202.703</t>
+          <t>1202708433.30692</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1401.437</t>
+          <t>1401487232.70585</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35826.052</t>
+          <t>35825476074.0129</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33691.691</t>
+          <t>33689464800.4829</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34289.44</t>
+          <t>34286973457.765</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34877.084</t>
+          <t>34876284983.2923</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>36012.595</t>
+          <t>36012409948.2546</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>38249.016</t>
+          <t>38248061167.4941</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>39156.271</t>
+          <t>39154607203.6885</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40126.535</t>
+          <t>40124060991.5379</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>42223.399</t>
+          <t>42221370903.0523</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>43389.734</t>
+          <t>43388078997.7498</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>45426.496</t>
+          <t>45422379639.217</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>46083.629</t>
+          <t>46077939664.3403</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>45783.831</t>
+          <t>45781334457.2812</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>46489.779</t>
+          <t>46489859551.0243</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>47744.302</t>
+          <t>47745417715.2571</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13800.011</t>
+          <t>13799278342.8518</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14087.423</t>
+          <t>14084425974.0694</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14955.311</t>
+          <t>14952934678.4297</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16222.366</t>
+          <t>16220383799.8331</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17367.914</t>
+          <t>17366172355.4363</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18101.283</t>
+          <t>18099436327.6981</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18751.059</t>
+          <t>18750449195.4044</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>18168.951</t>
+          <t>18165622928.2738</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>17520.912</t>
+          <t>17518967275.6011</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>16533.468</t>
+          <t>16532130772.7509</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>16185.977</t>
+          <t>16183123297.156</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17363.821</t>
+          <t>17359747266.5853</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17599.951</t>
+          <t>17598138625.333</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>17535.246</t>
+          <t>17534964835.4053</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>17142.978</t>
+          <t>17144112445.3604</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>502613.91</t>
+          <t>502601689259.991</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>509149.185</t>
+          <t>509122121759.879</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>527058.424</t>
+          <t>527032802402.347</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>510059.107</t>
+          <t>510049273702.906</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>508734.913</t>
+          <t>508726957492.146</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>490159.689</t>
+          <t>490154959977.541</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>499655.154</t>
+          <t>499644326274.245</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>484670.881</t>
+          <t>484642956847.919</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>534315.695</t>
+          <t>534315891329.701</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>570917.195</t>
+          <t>570906186436.344</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>568982.504</t>
+          <t>568953098882.618</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>603629.121</t>
+          <t>603569017220.243</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>640766.772</t>
+          <t>640737450899.619</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>623564.781</t>
+          <t>623560014684.789</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>625704.168</t>
+          <t>625720457189.654</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>253.945</t>
+          <t>253933121.171671</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>283.639</t>
+          <t>283594926.53438</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>343.046</t>
+          <t>342992967.209998</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>397.968</t>
+          <t>397935438.76706</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>393.254</t>
+          <t>393253194.470721</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>384.272</t>
+          <t>384259357.393815</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>359.05</t>
+          <t>359034686.091811</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>353.06</t>
+          <t>353013231.280435</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>415.609</t>
+          <t>415590065.643862</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>367.623</t>
+          <t>367601606.880447</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>369.801</t>
+          <t>369757181.85089</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>359.275</t>
+          <t>359220508.411182</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>325.3</t>
+          <t>325283230.991265</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>316.624</t>
+          <t>316619936.971819</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>307.43</t>
+          <t>307437229.995181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1639.897</t>
+          <t>1639863937.94268</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1642.68</t>
+          <t>1642610529.0481</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1757.676</t>
+          <t>1757409598.28783</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1876.254</t>
+          <t>1876057202.72793</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1927.784</t>
+          <t>1927828796.16483</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2046.723</t>
+          <t>2046672875.68442</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2030.977</t>
+          <t>2030935400.07947</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2074.855</t>
+          <t>2074465664.36433</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2154.922</t>
+          <t>2154675816.6072</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2004.088</t>
+          <t>2003604558.47391</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1948.724</t>
+          <t>1949133898.86183</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2079.913</t>
+          <t>2079507853.72554</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1976.967</t>
+          <t>1977823120.92538</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2080.777</t>
+          <t>2080239355.92722</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2020.977</t>
+          <t>2022204552.69788</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>39294.519</t>
+          <t>39281499232.5602</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37790.813</t>
+          <t>37811053687.526</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>37876.852</t>
+          <t>37854460550.8292</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>41829.607</t>
+          <t>41802364333.2831</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>42897.648</t>
+          <t>42928265410.9969</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>41469.927</t>
+          <t>41489156126.6315</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>42414.751</t>
+          <t>42406955608.3851</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>42665.415</t>
+          <t>42625675284.5456</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41554.235</t>
+          <t>41544197102.8095</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>39866.455</t>
+          <t>39864349565.5104</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>36193.966</t>
+          <t>36190657213.0254</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>39413.315</t>
+          <t>39408059573.2569</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>36816.269</t>
+          <t>36813654120.0613</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>40453.716</t>
+          <t>40453464005.5364</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>40983.153</t>
+          <t>40985049589.0034</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2973.427</t>
+          <t>2973257803.126</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3062.561</t>
+          <t>3062356960.32338</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3066.117</t>
+          <t>3065712856.69255</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3584.796</t>
+          <t>3584487499.57961</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3530.533</t>
+          <t>3530419025.25489</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3614.691</t>
+          <t>3614729506.68733</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3554.276</t>
+          <t>3554149703.42512</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3453.607</t>
+          <t>3452948919.0312</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3531.379</t>
+          <t>3530991773.55852</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3288.097</t>
+          <t>3287903127.74136</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3051.191</t>
+          <t>3050924187.26731</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2994.603</t>
+          <t>2994216007.88656</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2764.633</t>
+          <t>2764422291.38279</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2508.335</t>
+          <t>2508339907.46308</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2666.981</t>
+          <t>2666936245.48453</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12516.473</t>
+          <t>12515348334.8921</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13383.342</t>
+          <t>13382022053.7889</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14457.356</t>
+          <t>14456008610.3378</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16185.577</t>
+          <t>16184329980.1854</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17823.225</t>
+          <t>17822666074.3685</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>18401.433</t>
+          <t>18400993287.3298</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18660.954</t>
+          <t>18660523100.9168</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>19150.421</t>
+          <t>19149267049.9029</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>19779.129</t>
+          <t>19778290061.8718</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17652.586</t>
+          <t>17651665055.452</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>16130.699</t>
+          <t>16129372067.9217</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>16051.174</t>
+          <t>16050971286.4322</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>14095.829</t>
+          <t>14096203511.4385</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>14336.471</t>
+          <t>14337194403.4132</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>14760.859</t>
+          <t>14761777174.8412</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>307.35</t>
+          <t>307307801.836704</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>297.998</t>
+          <t>297933311.829424</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>366.831</t>
+          <t>366760034.141379</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>424.773</t>
+          <t>424639589.699971</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>399.654</t>
+          <t>399562857.163792</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>408.875</t>
+          <t>408836025.439322</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>497.049</t>
+          <t>496944182.746326</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>512.825</t>
+          <t>512760977.767353</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>527.872</t>
+          <t>527807856.695453</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>386.663</t>
+          <t>386623397.448879</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>337.653</t>
+          <t>337604064.714267</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>375.376</t>
+          <t>375271519.92863</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>363.117</t>
+          <t>363097430.485497</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>374.045</t>
+          <t>374063681.154138</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>436.315</t>
+          <t>436349549.214292</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1843.446</t>
+          <t>1842113949.99015</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1832.952</t>
+          <t>1831772662.09415</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1926.017</t>
+          <t>1925184755.28565</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2138.507</t>
+          <t>2138215003.83796</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2274.257</t>
+          <t>2274044536.89226</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2359.41</t>
+          <t>2359438587.27575</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2322.895</t>
+          <t>2323661246.88211</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2327.873</t>
+          <t>2327277415.93118</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2458.297</t>
+          <t>2457815972.18401</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2156.823</t>
+          <t>2156985231.37454</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1942.533</t>
+          <t>1942297781.03994</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1888.515</t>
+          <t>1888126100.42442</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1990.027</t>
+          <t>1989669722.99643</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2029.671</t>
+          <t>2029776522.55925</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1910.456</t>
+          <t>1910627624.85825</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>26374.426</t>
+          <t>26372019422.9433</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27086.414</t>
+          <t>27083369713.2043</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29140.802</t>
+          <t>29137345758.1091</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31916.306</t>
+          <t>31913709631.4038</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31905.036</t>
+          <t>31904650621.8544</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>31828.395</t>
+          <t>31826551472.4216</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>31006.372</t>
+          <t>31004979476.3919</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>30612.596</t>
+          <t>30607980534.1507</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30091.824</t>
+          <t>30088402273.5743</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>27784.965</t>
+          <t>27782671305.8272</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24643.317</t>
+          <t>24640900755.363</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26356.799</t>
+          <t>26354262352.3306</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24932.529</t>
+          <t>24932499751.053</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>25623.886</t>
+          <t>25625593052.0506</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>26563.515</t>
+          <t>26566575475.4961</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29806.385</t>
+          <t>29803589465.7681</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31923.763</t>
+          <t>31919459128.1563</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33912.808</t>
+          <t>33908040718.6579</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34700.381</t>
+          <t>34696836677.7945</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>37716.088</t>
+          <t>37714407223.0423</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>37944.441</t>
+          <t>37942587597.7036</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>38647.625</t>
+          <t>38645943058.169</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>36096.554</t>
+          <t>36092166129.0391</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>32063.037</t>
+          <t>32059821527.4573</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29155.931</t>
+          <t>29155011327.5037</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>26093.852</t>
+          <t>26090815444.9198</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>25464.028</t>
+          <t>25460750184.3769</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>25821.591</t>
+          <t>25820028821.9183</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>29926.225</t>
+          <t>29926951949.2679</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>24922.072</t>
+          <t>24922950238.8031</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2345.829</t>
+          <t>2345803714.04368</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2317.725</t>
+          <t>2317502714.19332</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2511.769</t>
+          <t>2511440257.62385</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2776.262</t>
+          <t>2776061383.21948</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2895.056</t>
+          <t>2894915552.00543</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3071.444</t>
+          <t>3071620395.78496</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3237.878</t>
+          <t>3237723722.59939</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3316.263</t>
+          <t>3315986252.67453</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3330.185</t>
+          <t>3329865978.26457</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3259.905</t>
+          <t>3259654351.8545</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2815.827</t>
+          <t>2815500602.04227</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2629.693</t>
+          <t>2629410281.00747</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2151.981</t>
+          <t>2151833975.92363</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026.404</t>
+          <t>2026144927.01421</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2063.932</t>
+          <t>2063891440.45435</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2000.17</t>
+          <t>1999963233.34973</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2045.356</t>
+          <t>2045024048.45562</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2195.624</t>
+          <t>2195185661.03394</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2288.122</t>
+          <t>2287727257.69535</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2134.28</t>
+          <t>2134135712.46185</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2031.616</t>
+          <t>2031517900.68685</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1957.198</t>
+          <t>1956853416.78495</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1885.088</t>
+          <t>1884662634.43198</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1827.541</t>
+          <t>1827808515.14141</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1729.932</t>
+          <t>1729885465.67635</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1483.592</t>
+          <t>1483258675.12768</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1479.505</t>
+          <t>1479118578.72673</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1395.811</t>
+          <t>1395718928.77889</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1416.784</t>
+          <t>1416792768.55772</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1552.489</t>
+          <t>1552741289.75753</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>28611.632</t>
+          <t>28611423056.2854</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30545.224</t>
+          <t>30544630510.3717</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31218.443</t>
+          <t>31217828095.0702</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>36251.097</t>
+          <t>36250532693.5276</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>37035.301</t>
+          <t>37034443788.5825</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>34797.984</t>
+          <t>34797518518.4153</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>33163.643</t>
+          <t>33163348597.8868</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>34000.298</t>
+          <t>33999857600.7279</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>33261.233</t>
+          <t>33260404381.6169</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>36183.199</t>
+          <t>36182746238.1147</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>37114.124</t>
+          <t>37112772635.4446</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>37749.556</t>
+          <t>37747551478.6751</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>40595.486</t>
+          <t>40594814052.9312</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>43946.903</t>
+          <t>43946760039.3078</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>48668.046</t>
+          <t>48668955744.7654</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>189570.321</t>
+          <t>189567016183.62</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>187155.714</t>
+          <t>187148493039.284</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>186671.186</t>
+          <t>186665942178.39</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>187705.421</t>
+          <t>187702772529.028</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>184930.821</t>
+          <t>184929668364.014</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>186868.916</t>
+          <t>186868125932.169</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>185021.452</t>
+          <t>185015270401.296</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>189025.774</t>
+          <t>189020258085.998</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>186711.658</t>
+          <t>186719277093.469</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>191182.623</t>
+          <t>191181109110.828</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>187841.283</t>
+          <t>187835182669.242</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>192533.713</t>
+          <t>192524358647.887</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>209722.628</t>
+          <t>209718915739.687</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>229190.16</t>
+          <t>229189494877.86</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>245016.423</t>
+          <t>245020325849.135</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1166.896</t>
+          <t>1166789344.91951</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1430.469</t>
+          <t>1430251240.46789</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1526.727</t>
+          <t>1526528501.50392</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1531.221</t>
+          <t>1531023956.51964</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1797.951</t>
+          <t>1797811694.65433</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2003.033</t>
+          <t>2002935046.62543</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2136.371</t>
+          <t>2136299289.31334</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2132.746</t>
+          <t>2132378954.73743</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2098.786</t>
+          <t>2098622136.7335</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1612.838</t>
+          <t>1612724369.25588</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>998.967</t>
+          <t>998769543.005397</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1384.326</t>
+          <t>1384017700.53913</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1296.773</t>
+          <t>1296651190.89904</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1349.449</t>
+          <t>1349440334.65467</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1257.888</t>
+          <t>1258064922.56275</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15351.52</t>
+          <t>15350446824.2959</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15928.62</t>
+          <t>15927908894.9524</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>16736.968</t>
+          <t>16734048714.2276</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18395.495</t>
+          <t>18393313889.282</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>19714.664</t>
+          <t>19713873554.7992</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>19816.589</t>
+          <t>19816016553.1756</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20854.002</t>
+          <t>20853089577.3987</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>19761.707</t>
+          <t>19759700666.9134</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>20000.757</t>
+          <t>20000311927.5603</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>17937.845</t>
+          <t>17936123262.8955</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17081.58</t>
+          <t>17080778269.0785</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17456.839</t>
+          <t>17455212834.0171</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>15360.157</t>
+          <t>15359734882.7878</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>14944.659</t>
+          <t>14944986550.5006</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>15232.965</t>
+          <t>15234394318.998</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>77077.223</t>
+          <t>77081965805.8465</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>73233.861</t>
+          <t>73166260233.7656</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>69695.882</t>
+          <t>69636804715.4756</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71824.384</t>
+          <t>71775833056.1982</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>74127.439</t>
+          <t>74073612660.8939</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>73773.413</t>
+          <t>73723395637.7857</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>72118.043</t>
+          <t>72166445323.0391</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>63347.16</t>
+          <t>63337574217.7434</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>61627.266</t>
+          <t>61617407386.345</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59067.759</t>
+          <t>59110835796.35</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>57496.765</t>
+          <t>57493645267.3246</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>62840.317</t>
+          <t>62774548209.2356</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>60662.938</t>
+          <t>60611719008.2791</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>56356.386</t>
+          <t>56332525960.778</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>55180.497</t>
+          <t>55128667483.2789</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14056.78</t>
+          <t>14055902905.5326</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14693.85</t>
+          <t>14689209162.704</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15642.221</t>
+          <t>15637869451.7607</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17031.544</t>
+          <t>17029272070.728</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>18617.998</t>
+          <t>18614872603.3885</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18464.343</t>
+          <t>18463045946.9007</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>18973.815</t>
+          <t>18972593376.3608</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>18067.891</t>
+          <t>18062985799.9901</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>17720.439</t>
+          <t>17721574513.3457</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17649.456</t>
+          <t>17649020797.1722</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17896.431</t>
+          <t>17893185421.7562</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19493.293</t>
+          <t>19487485055.0695</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20632.27</t>
+          <t>20629227497.5971</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>22159.576</t>
+          <t>22159927284.2208</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>22934.342</t>
+          <t>22936687955.0425</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>847.595</t>
+          <t>847663943.452968</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>834.18</t>
+          <t>834010467.594517</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>898.127</t>
+          <t>898064298.170487</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>989.962</t>
+          <t>990064817.642034</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>911.935</t>
+          <t>911963837.335983</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>935.911</t>
+          <t>935726710.613234</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1051.476</t>
+          <t>1051249439.12176</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>997.946</t>
+          <t>997722114.019014</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1059.732</t>
+          <t>1059715628.99606</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>865.654</t>
+          <t>865667502.678305</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>710.819</t>
+          <t>710731796.049489</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>785.044</t>
+          <t>784951370.832772</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>772.54</t>
+          <t>772730149.933276</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>843.691</t>
+          <t>843916284.381719</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>907.436</t>
+          <t>907518753.379963</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>261.394</t>
+          <t>261355485.255603</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>272.463</t>
+          <t>272448218.335439</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>296.137</t>
+          <t>296066020.091404</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>314.086</t>
+          <t>314001918.574562</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>339.314</t>
+          <t>339315485.617356</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>367.543</t>
+          <t>367554157.842774</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>396.722</t>
+          <t>396705451.864302</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>374.642</t>
+          <t>374516107.035379</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>489.54</t>
+          <t>489490117.630874</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>542.595</t>
+          <t>542552703.149704</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>532.045</t>
+          <t>531971510.071077</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>562.602</t>
+          <t>562487989.439198</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>520.471</t>
+          <t>520436805.911152</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>530.325</t>
+          <t>530312851.99769</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>575.75</t>
+          <t>575849027.224523</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>576.972</t>
+          <t>576938089.972479</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>587.41</t>
+          <t>587351933.110709</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>578.206</t>
+          <t>578169821.533441</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>620.21</t>
+          <t>620185176.534206</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>599.238</t>
+          <t>599230239.197004</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>625.266</t>
+          <t>625246028.843624</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>730.118</t>
+          <t>730050972.537691</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>798.811</t>
+          <t>798718914.309656</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>796.407</t>
+          <t>796422019.291755</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>568.084</t>
+          <t>568067245.48428</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>436.132</t>
+          <t>436069133.317561</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>458.665</t>
+          <t>458574640.763162</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>467.138</t>
+          <t>467130109.770779</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>470.786</t>
+          <t>470793445.7199</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>519.008</t>
+          <t>519048385.308023</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10919.16</t>
+          <t>10918833316.9135</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>11627.375</t>
+          <t>11626129153.9358</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>12162.978</t>
+          <t>12161722200.5059</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11911.637</t>
+          <t>11911055788.6686</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>11548.954</t>
+          <t>11548589966.3917</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>11569.028</t>
+          <t>11568388393.2323</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11675.046</t>
+          <t>11674263685.269</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>11729.112</t>
+          <t>11727709496.4837</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>11306.196</t>
+          <t>11306190129.7508</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>11035.66</t>
+          <t>11035369500.4475</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10968.666</t>
+          <t>10967743199.983</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10930.083</t>
+          <t>10928692567.2892</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11163.307</t>
+          <t>11162798769.7275</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>11403.232</t>
+          <t>11403096530.9203</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>11413.022</t>
+          <t>11413188131.449</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>106.605</t>
+          <t>106598549.463612</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>110.268</t>
+          <t>110253976.81798</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>115.958</t>
+          <t>115936708.53716</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>136.538</t>
+          <t>136525982.597501</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>128.633</t>
+          <t>128630446.276401</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>142.325</t>
+          <t>142318857.710135</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>138.181</t>
+          <t>138176105.393315</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>134.832</t>
+          <t>134807248.697673</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>153.437</t>
+          <t>153417062.937035</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>140.303</t>
+          <t>140290382.139663</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>131.327</t>
+          <t>131308703.210382</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>133.993</t>
+          <t>133962565.323281</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>137.328</t>
+          <t>137311918.724648</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>138.998</t>
+          <t>138998921.292378</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>136.723</t>
+          <t>136733175.270774</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>13308.088</t>
+          <t>13307667510.7618</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12872.534</t>
+          <t>12871978866.151</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13394.602</t>
+          <t>13393482078.2862</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12614.339</t>
+          <t>12613499952.0852</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12047.589</t>
+          <t>12047904869.2236</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>11486.499</t>
+          <t>11486435653.3957</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11690.256</t>
+          <t>11689850184.3022</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12160.664</t>
+          <t>12159230758.6891</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13033.611</t>
+          <t>13032977189.9364</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>11512.044</t>
+          <t>11512246382.3452</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>9311.557</t>
+          <t>9310357076.91389</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>9208.593</t>
+          <t>9207121401.60207</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8648.76</t>
+          <t>8647662522.27098</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>12158.885</t>
+          <t>12158196354.9385</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>12062.644</t>
+          <t>12063565652.1724</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7353.776</t>
+          <t>7353551284.12591</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8041.786</t>
+          <t>8041379237.46016</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6943.59</t>
+          <t>6943121111.39288</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6686.971</t>
+          <t>6686566800.43728</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6462.394</t>
+          <t>6462308279.32439</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6604.295</t>
+          <t>6604158844.08749</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6682.947</t>
+          <t>6682682460.02708</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6998.978</t>
+          <t>6998234869.15329</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7844.64</t>
+          <t>7844571944.77436</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>7085.288</t>
+          <t>7085058645.30157</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>7172.008</t>
+          <t>7171345633.0823</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>7276.904</t>
+          <t>7276033865.10395</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>7012.765</t>
+          <t>7012473947.36348</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>7263.445</t>
+          <t>7263450101.24057</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>7438.142</t>
+          <t>7438655948.4522</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3849.499</t>
+          <t>3849321268.20304</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3943.755</t>
+          <t>3943509518.60329</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3847.008</t>
+          <t>3846649466.07221</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3960.701</t>
+          <t>3960429318.29895</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4017.096</t>
+          <t>4017091200.28422</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3941.184</t>
+          <t>3941117541.38827</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3777.037</t>
+          <t>3776863033.5717</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3670.828</t>
+          <t>3670598254.9674</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3732.273</t>
+          <t>3732145040.98328</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3378.896</t>
+          <t>3378720145.92696</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>3217.864</t>
+          <t>3217500546.82023</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3276.147</t>
+          <t>3275792164.50829</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3018.827</t>
+          <t>3018711142.67874</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3009.971</t>
+          <t>3010009949.48095</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2968.555</t>
+          <t>2968807419.66129</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7162.892</t>
+          <t>7162799723.85714</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7144.284</t>
+          <t>7144102043.52001</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5638.239</t>
+          <t>5637990283.68396</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5804.915</t>
+          <t>5804778679.87063</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5264.464</t>
+          <t>5264454114.43731</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6006.876</t>
+          <t>6006781034.59423</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6063.294</t>
+          <t>6062782646.24209</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6156.993</t>
+          <t>6156470394.2109</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6405.77</t>
+          <t>6406432023.14219</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5781.094</t>
+          <t>5780968526.2417</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>5339.744</t>
+          <t>5339354054.29117</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>4887.364</t>
+          <t>4887023169.45075</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>3600.267</t>
+          <t>3600171327.08127</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>3409.842</t>
+          <t>3409828644.83589</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>3710.85</t>
+          <t>3710947187.34471</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>44599.48</t>
+          <t>44598332642.8781</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>44759.562</t>
+          <t>44755613499.9693</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>46820.961</t>
+          <t>46817255469.9241</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50946.889</t>
+          <t>50944761065.5864</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>53930.817</t>
+          <t>53930404750.7182</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>56402.903</t>
+          <t>56400962183.7704</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>57320.655</t>
+          <t>57315554263.846</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>62611.907</t>
+          <t>62606176261.7769</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>59015.029</t>
+          <t>59020018090.6854</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>59649.838</t>
+          <t>59648945625.9844</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>64364.412</t>
+          <t>64359539831.3348</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>63396.06</t>
+          <t>63389782792.0459</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>69798.126</t>
+          <t>69794770159.7811</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>69422.697</t>
+          <t>69422655936.7061</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>59862.93</t>
+          <t>59864133532.5563</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>887.386</t>
+          <t>887354532.880413</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>845.848</t>
+          <t>845687677.410025</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>861.379</t>
+          <t>861284145.749882</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>899.436</t>
+          <t>899555715.438676</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1090.206</t>
+          <t>1090320068.45285</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1149.28</t>
+          <t>1149255817.6423</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1268.892</t>
+          <t>1268869758.46601</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1511.945</t>
+          <t>1512532355.7828</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1446.023</t>
+          <t>1446095436.42002</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1593.293</t>
+          <t>1593207686.35224</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1371.351</t>
+          <t>1371067424.10509</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1428.982</t>
+          <t>1428681505.82526</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1531.233</t>
+          <t>1531168288.08007</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1608.591</t>
+          <t>1608565811.00264</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1639.911</t>
+          <t>1640018888.47212</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>730.654</t>
+          <t>730632531.205339</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>746.326</t>
+          <t>746373014.574136</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>753.734</t>
+          <t>753686180.3853</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>839.508</t>
+          <t>839479862.121275</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>985.667</t>
+          <t>985778034.104179</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1008.668</t>
+          <t>1008760777.16025</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1025.488</t>
+          <t>1025476054.96869</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1030.161</t>
+          <t>1029934783.50664</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1066.694</t>
+          <t>1066530614.18038</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1066.353</t>
+          <t>1066206100.9408</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>969.128</t>
+          <t>968943275.609179</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1003.47</t>
+          <t>1003250259.66449</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>953.598</t>
+          <t>953466185.664021</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>934.724</t>
+          <t>934692445.413795</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>946.549</t>
+          <t>946597829.092537</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4083.848</t>
+          <t>4083331274.86911</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4076.103</t>
+          <t>4075173123.18216</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4166.124</t>
+          <t>4165644181.30612</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4430.687</t>
+          <t>4429852955.03918</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4708.223</t>
+          <t>4707639602.06336</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4586.277</t>
+          <t>4585902722.7027</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4581.653</t>
+          <t>4581312280.77724</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4554.149</t>
+          <t>4553217965.15053</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4561.278</t>
+          <t>4561047518.39094</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4132.208</t>
+          <t>4131898499.94978</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>3795.893</t>
+          <t>3795039562.32228</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4299.671</t>
+          <t>4298607697.07757</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4042.077</t>
+          <t>4041867467.41596</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4300.948</t>
+          <t>4300728172.07739</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4273.535</t>
+          <t>4274540446.19049</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8747.095</t>
+          <t>8746697254.71349</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8408.936</t>
+          <t>8407973396.525</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7531.582</t>
+          <t>7530769150.99101</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7698.138</t>
+          <t>7697643541.5513</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>8283.161</t>
+          <t>8282914899.00648</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>8050.893</t>
+          <t>8050811223.8915</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7760.331</t>
+          <t>7759620079.09678</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7698.165</t>
+          <t>7697168123.55752</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>7757.295</t>
+          <t>7757729063.21871</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>7211.382</t>
+          <t>7210843352.46181</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>8012.093</t>
+          <t>8010450380.33574</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>8769.952</t>
+          <t>8768051202.55762</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>9047.748</t>
+          <t>9046489562.34209</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>9399.615</t>
+          <t>9400062084.96689</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>10166.523</t>
+          <t>10167310773.3096</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12095.022</t>
+          <t>12094108515.4398</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11602.969</t>
+          <t>11599226749.3497</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>12141.184</t>
+          <t>12137708052.0434</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>12565.577</t>
+          <t>12563723262.6112</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>12839.887</t>
+          <t>12837377108.054</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12885.79</t>
+          <t>12884643281.9988</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>12786.862</t>
+          <t>12787439570.9758</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12125.91</t>
+          <t>12123450875.8004</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>11653.859</t>
+          <t>11652994850.8607</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>11075.042</t>
+          <t>11074932202.3799</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11448.859</t>
+          <t>11447475308.8852</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11542.618</t>
+          <t>11539263892.8553</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11305.473</t>
+          <t>11303919892.0013</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>10741.856</t>
+          <t>10741520729.9815</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>11536.897</t>
+          <t>11537277687.7904</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>159922.399</t>
+          <t>159900922369.627</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>163183.912</t>
+          <t>163137326783.243</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>168288.379</t>
+          <t>168254751820.254</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>171437.537</t>
+          <t>171409666377.047</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>174461.439</t>
+          <t>174430058068.356</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>178350.677</t>
+          <t>178349814481.85</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>176717.382</t>
+          <t>176711982627.7</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>164294.24</t>
+          <t>164253229073.529</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>153797.292</t>
+          <t>153791611142.949</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>140905.354</t>
+          <t>140897822960.685</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>136682.053</t>
+          <t>136647693950.259</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>139060.172</t>
+          <t>138995921621.83</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>141892.873</t>
+          <t>141872650269.406</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>139721.128</t>
+          <t>139712066481.26</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>142492.2</t>
+          <t>142521426334.282</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>784145.643</t>
+          <t>784137847169.266</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>793783.161</t>
+          <t>793756301921.496</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>843291.321</t>
+          <t>843267758953.288</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>852325.494</t>
+          <t>852304675381.817</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>835279.28</t>
+          <t>835259375511.156</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>865014.563</t>
+          <t>864995539184.223</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>892263.011</t>
+          <t>892235073256.426</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>860580.123</t>
+          <t>860552604730.381</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>871091.336</t>
+          <t>871108774400.428</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>884945.85</t>
+          <t>884939209251.114</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>863456.849</t>
+          <t>863424222697.806</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>863065.165</t>
+          <t>863017607364.134</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>915735.237</t>
+          <t>915715741886.067</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>948179.837</t>
+          <t>948180867772.27</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>977060.384</t>
+          <t>977074465481.708</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2084936.279</t>
+          <t>2084863820621.48</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2102073.868</t>
+          <t>2101880171784.76</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2182191.487</t>
+          <t>2181979998502.07</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2208467.068</t>
+          <t>2208300955080.61</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2209677.18</t>
+          <t>2209576968060.04</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2229823.532</t>
+          <t>2229753162592.01</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2265198.756</t>
+          <t>2265171382121.82</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2204421.855</t>
+          <t>2204222937125.17</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2242645.991</t>
+          <t>2242636188408.45</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2267177.05</t>
+          <t>2267176826425.66</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2223712.328</t>
+          <t>2223565892885.32</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2282378.811</t>
+          <t>2282072349236.77</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2388280.219</t>
+          <t>2388132108917.47</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2435136.303</t>
+          <t>2435099776162.26</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2480107.988</t>
+          <t>2480147168831.98</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1063.52</t>
+          <t>1063488230.90022</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>997.039</t>
+          <t>996982615.810266</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1103.116</t>
+          <t>1103003107.61181</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1129.992</t>
+          <t>1129911860.65422</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1232.457</t>
+          <t>1232457279.83393</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1259.359</t>
+          <t>1259351363.71908</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1319.459</t>
+          <t>1319401527.87821</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1388.279</t>
+          <t>1388107686.26846</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1486.963</t>
+          <t>1486894693.56668</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1394.057</t>
+          <t>1393991378.00972</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1270.214</t>
+          <t>1270083920.42409</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1199.064</t>
+          <t>1198891166.15013</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1104.751</t>
+          <t>1104695482.03829</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1004.792</t>
+          <t>1004787981.45389</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>945.485</t>
+          <t>945537704.002765</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4786.923</t>
+          <t>4785874308.72674</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4654.408</t>
+          <t>4653695644.66312</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4707.963</t>
+          <t>4706916034.45597</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>5006.151</t>
+          <t>5005106904.36969</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4808.478</t>
+          <t>4808085068.87083</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>4788.055</t>
+          <t>4788864832.69186</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>4810.139</t>
+          <t>4809780559.83565</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>4632.177</t>
+          <t>4630667736.18824</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4837.716</t>
+          <t>4838437146.53653</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4595.27</t>
+          <t>4595500213.52908</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>4652.214</t>
+          <t>4651585693.14333</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>5150.7</t>
+          <t>5148735457.24906</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>5075.758</t>
+          <t>5074920275.94052</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>5332.645</t>
+          <t>5332236739.04129</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>5383.875</t>
+          <t>5385395986.92456</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2741.309</t>
+          <t>2741088835.57762</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2859.475</t>
+          <t>2858978580.17506</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3000.298</t>
+          <t>2999850482.22913</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3066.857</t>
+          <t>3066344972.91229</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3298.455</t>
+          <t>3298193073.16132</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3304.827</t>
+          <t>3304590093.66772</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3450.037</t>
+          <t>3449733097.40449</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3610.65</t>
+          <t>3609879116.67003</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3688.957</t>
+          <t>3688840560.97476</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3548.203</t>
+          <t>3548039263.6648</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3223.105</t>
+          <t>3222577785.47051</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3616.979</t>
+          <t>3616284551.75609</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3360.782</t>
+          <t>3360507082.47205</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>3735.256</t>
+          <t>3735218455.16124</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3762.522</t>
+          <t>3762762713.50427</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
